--- a/nr-update-practitioner-qualification-reslice/ig/ValueSet-fr-core-vs-organization-uf-activity-field.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/ValueSet-fr-core-vs-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:45:11+00:00</t>
+    <t>2025-07-08T14:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-practitioner-qualification-reslice/ig/ValueSet-fr-core-vs-organization-uf-activity-field.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/ValueSet-fr-core-vs-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:52:18+00:00</t>
+    <t>2025-07-10T12:55:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
